--- a/ClosedXML.Tests/Resource/Examples/PivotTables/PivotTables.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/PivotTables/PivotTables.xlsx
@@ -81,9 +81,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="164" formatCode="0%"/>
   </x:numFmts>
   <x:fonts count="1">
     <x:font>
@@ -178,7 +177,7 @@
     <field x="4"/>
   </colFields>
   <dataFields count="1">
-    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="164"/>
+    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="9"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
   <extLst>
@@ -299,7 +298,7 @@
     <field x="4"/>
   </colFields>
   <dataFields count="2">
-    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="164"/>
+    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="9"/>
     <dataField name="Sum of Quality" fld="3" numFmtId="4"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
@@ -345,7 +344,7 @@
     <field x="-2"/>
   </colFields>
   <dataFields count="3">
-    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="164"/>
+    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="9"/>
     <dataField name="Sum of Quality" fld="3" numFmtId="4"/>
     <dataField name="Sum of NumberOfOrders" fld="2"/>
   </dataFields>
@@ -526,7 +525,7 @@
     <field x="0"/>
   </colFields>
   <dataFields count="2">
-    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="164"/>
+    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="9"/>
     <dataField name="Sum of Quality" fld="3" numFmtId="4"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
